--- a/server/assets/template_soh.xlsx
+++ b/server/assets/template_soh.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
-    <t xml:space="preserve">(Дата соcтавления)</t>
+    <t xml:space="preserve">(Дата сотавления)</t>
   </si>
   <si>
     <t xml:space="preserve">(Место составления)</t>
@@ -881,10 +881,7 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="Z2" s="2" t="str">
-        <f aca="false">CONCATENATE("*",AT11,"*")</f>
-        <v>**</v>
-      </c>
+      <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -2972,9 +2969,7 @@
       <c r="BP33" s="22"/>
       <c r="BQ33" s="22"/>
       <c r="BR33" s="22"/>
-      <c r="BS33" s="23" t="n">
-        <v>1</v>
-      </c>
+      <c r="BS33" s="23"/>
       <c r="BT33" s="23"/>
       <c r="BU33" s="23"/>
       <c r="BV33" s="23"/>

--- a/server/assets/template_soh.xlsx
+++ b/server/assets/template_soh.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="АКТ" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="buffer" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Лист1" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>

--- a/server/assets/template_soh.xlsx
+++ b/server/assets/template_soh.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
-    <t xml:space="preserve">(Дата сотавления)</t>
+    <t xml:space="preserve">(Дата соcтавления)</t>
   </si>
   <si>
     <t xml:space="preserve">(Место составления)</t>
@@ -624,7 +624,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2969,7 +2969,9 @@
       <c r="BP33" s="22"/>
       <c r="BQ33" s="22"/>
       <c r="BR33" s="22"/>
-      <c r="BS33" s="23"/>
+      <c r="BS33" s="23" t="n">
+        <v>1</v>
+      </c>
       <c r="BT33" s="23"/>
       <c r="BU33" s="23"/>
       <c r="BV33" s="23"/>
